--- a/01-Dia-Academico-Jueves-01-Oct/itinerario-dia-academico.xlsx
+++ b/01-Dia-Academico-Jueves-01-Oct/itinerario-dia-academico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Benjamín Ayala\Documents\B23 - Semana Cultural\01-Dia-Academico-Jueves-01-Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B10835-209E-4007-8DF5-C5BA78DD203C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D209F56-3909-4E2C-B6F0-19BCC808D0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>Itinerario — Día Académico</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Semana Cultural del Aniversario 45 — Bachillerato 23, Universidad de Colima</t>
+  </si>
+  <si>
+    <t>Taller videncial [3]</t>
   </si>
 </sst>
 </file>
@@ -296,51 +299,51 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -697,73 +700,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" s="7" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:6" s="7" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -780,69 +783,69 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>11</v>
+      <c r="F9" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -857,111 +860,102 @@
       <c r="E13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C1:F2"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
@@ -972,6 +966,15 @@
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
